--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1307-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1307-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD2C4AA3-0FAD-4ECB-84D6-DE9E0EB543ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{039913BA-070F-4C19-8F6D-AB05C41548B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4FA6FC9A-3EE6-4B16-9F3E-DF8F9537D6A1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C4DFF9FC-5DF2-45FD-A350-50F55246A0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="1307-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1595,26 +1595,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573B8FC9-2382-4EF4-BAAA-14720B5D2999}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E5E63F5-F7CA-4D02-A254-EE2DF8045BE6}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1647,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1684,7 +1683,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1736,7 +1735,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1804,7 +1803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1876,7 +1875,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2020,7 +2019,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2092,7 +2091,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2164,7 +2163,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2236,7 +2235,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2018</v>
       </c>
@@ -2308,7 +2307,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2016</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2015</v>
       </c>
@@ -2524,7 +2523,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2668,7 +2667,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2012</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="43">
         <v>2011</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="45"/>
       <c r="B19" s="46"/>
       <c r="C19" s="20" t="s">
@@ -2840,7 +2839,7 @@
       <c r="W19" s="52"/>
       <c r="X19" s="48"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>2010</v>
       </c>
@@ -2912,7 +2911,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="55"/>
       <c r="B21" s="56"/>
       <c r="C21" s="22" t="s">
@@ -2940,7 +2939,7 @@
       <c r="W21" s="62"/>
       <c r="X21" s="58"/>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="43">
         <v>2009</v>
       </c>
@@ -3012,7 +3011,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="45"/>
       <c r="B23" s="46"/>
       <c r="C23" s="20" t="s">
@@ -3040,7 +3039,7 @@
       <c r="W23" s="52"/>
       <c r="X23" s="48"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2008</v>
       </c>
@@ -3112,7 +3111,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43">
         <v>2007</v>
       </c>
@@ -3184,7 +3183,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
       <c r="C26" s="20" t="s">
@@ -3212,7 +3211,7 @@
       <c r="W26" s="52"/>
       <c r="X26" s="48"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2006</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2005</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2004</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>2003</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2002</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>2001</v>
       </c>
@@ -3644,7 +3643,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>2000</v>
       </c>
@@ -3716,7 +3715,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>1999</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1998</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>1997</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1996</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1995</v>
       </c>
@@ -4076,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1994</v>
       </c>
@@ -4148,7 +4147,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>1993</v>
       </c>
@@ -4220,7 +4219,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1992</v>
       </c>
@@ -4292,7 +4291,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>1991</v>
       </c>
@@ -4364,7 +4363,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1990</v>
       </c>
@@ -4436,7 +4435,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1989</v>
       </c>
@@ -4508,7 +4507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1988</v>
       </c>
@@ -4580,7 +4579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>1987</v>
       </c>
@@ -4652,7 +4651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>1986</v>
       </c>
@@ -4724,7 +4723,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>1985</v>
       </c>
@@ -4796,7 +4795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>1984</v>
       </c>
@@ -4868,7 +4867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="41">
         <v>1983</v>
       </c>
@@ -4940,7 +4939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39" t="s">
         <v>65</v>
       </c>
